--- a/20260119.xlsx
+++ b/20260119.xlsx
@@ -162,7 +162,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1" style="0" width="8.67"/>
@@ -199,7 +199,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>10</v>
@@ -228,13 +228,13 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>0</v>
@@ -257,13 +257,13 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>0</v>
@@ -286,7 +286,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>0</v>
@@ -315,16 +315,16 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>0</v>
@@ -344,16 +344,16 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>0</v>
@@ -373,7 +373,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>0</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>0</v>
@@ -411,10 +411,10 @@
         <v>0</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9" s="0" t="n">
         <v>0</v>
@@ -431,7 +431,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>0</v>
@@ -440,10 +440,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F10" s="0" t="n">
         <v>0</v>
@@ -460,7 +460,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>0</v>
@@ -489,7 +489,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>0</v>
@@ -501,10 +501,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G12" s="0" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>0</v>
@@ -530,10 +530,10 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F13" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G13" s="0" t="n">
         <v>0</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>0</v>
@@ -576,13 +576,13 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G15" s="0" t="n">
         <v>0</v>
@@ -600,18 +600,18 @@
         <v>0</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>0</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G16" s="0" t="n">
         <v>0</v>
@@ -629,21 +629,21 @@
         <v>0</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E17" s="0" t="n">
         <v>0</v>
@@ -663,16 +663,16 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E18" s="0" t="n">
         <v>0</v>
@@ -692,10 +692,10 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>0</v>
@@ -707,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G19" s="0" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>0</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G20" s="0" t="n">
         <v>0</v>
@@ -750,7 +750,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>0</v>
@@ -806,64 +806,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -879,8 +823,8 @@
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
